--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Proposta por vendedor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38F3E65D-B90F-4399-A13F-EC76C8462F75}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{298D55C1-44B4-4572-9753-8CFD98C458F0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
     <sheet name="Como preencher" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -849,65 +862,67 @@
         <v>0</v>
       </c>
       <c r="C3" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J3" s="6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K3" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="6">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="O3" s="6">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="P3" s="6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R3" s="6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="V3" s="6">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="W3" s="6">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="X3" s="6">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="Y3" s="6">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
-      <c r="AB3" s="6"/>
+      <c r="AB3" s="6">
+        <v>6</v>
+      </c>
       <c r="AC3" s="6"/>
       <c r="AD3" s="6"/>
       <c r="AE3" s="6"/>
@@ -918,68 +933,70 @@
         <v>46</v>
       </c>
       <c r="B4" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O4" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P4" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R4" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
       <c r="U4" s="6">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V4" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="W4" s="6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="X4" s="6">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
-      <c r="AB4" s="6"/>
+      <c r="AB4" s="6">
+        <v>2</v>
+      </c>
       <c r="AC4" s="6"/>
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
@@ -990,68 +1007,70 @@
         <v>47</v>
       </c>
       <c r="B5" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H5" s="6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I5" s="6">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J5" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K5" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="6">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O5" s="6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="P5" s="6">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R5" s="6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="6">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="V5" s="6">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="W5" s="6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="X5" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="6">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
-      <c r="AB5" s="6"/>
+      <c r="AB5" s="6">
+        <v>1</v>
+      </c>
       <c r="AC5" s="6"/>
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
@@ -1068,62 +1087,64 @@
         <v>2</v>
       </c>
       <c r="D6" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H6" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K6" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O6" s="6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R6" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
       <c r="U6" s="6">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="V6" s="6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="W6" s="6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="X6" s="6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
-      <c r="AB6" s="6"/>
+      <c r="AB6" s="6">
+        <v>2</v>
+      </c>
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
@@ -1140,62 +1161,64 @@
         <v>1</v>
       </c>
       <c r="D7" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K7" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O7" s="6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P7" s="6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R7" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
       <c r="U7" s="6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="V7" s="6">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W7" s="6">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="X7" s="6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Y7" s="6">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="6"/>
+      <c r="AB7" s="6">
+        <v>2</v>
+      </c>
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
       <c r="AE7" s="6"/>
@@ -1212,62 +1235,64 @@
         <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P8" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
       <c r="U8" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V8" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W8" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X8" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="6"/>
+      <c r="AB8" s="6">
+        <v>1</v>
+      </c>
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
@@ -1278,7 +1303,7 @@
         <v>49</v>
       </c>
       <c r="B9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -1289,57 +1314,59 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I9" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J9" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K9" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O9" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P9" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R9" s="6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
       <c r="U9" s="6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="V9" s="6">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W9" s="6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="X9" s="6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Y9" s="6">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="6"/>
+      <c r="AB9" s="6">
+        <v>4</v>
+      </c>
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
@@ -1373,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -1384,34 +1411,36 @@
         <v>0</v>
       </c>
       <c r="P10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
       <c r="U10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
-      <c r="AB10" s="6"/>
+      <c r="AB10" s="6">
+        <v>0</v>
+      </c>
       <c r="AC10" s="6"/>
       <c r="AD10" s="6"/>
       <c r="AE10" s="6"/>
@@ -1425,7 +1454,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6">
         <v>0</v>
@@ -1433,57 +1462,59 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O11" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P11" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R11" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="6">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="V11" s="6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="W11" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="X11" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="6"/>
+      <c r="AB11" s="6">
+        <v>1</v>
+      </c>
       <c r="AC11" s="6"/>
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
@@ -1505,57 +1536,59 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="6">
         <v>4</v>
       </c>
       <c r="I12" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J12" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K12" s="6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O12" s="6">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="P12" s="6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="Q12" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R12" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
       <c r="U12" s="6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V12" s="6">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="W12" s="6">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="X12" s="6">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="Y12" s="6">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
-      <c r="AB12" s="6"/>
+      <c r="AB12" s="6">
+        <v>1</v>
+      </c>
       <c r="AC12" s="6"/>
       <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Proposta por vendedor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{298D55C1-44B4-4572-9753-8CFD98C458F0}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5B17DA-1C4E-4520-9BCA-7D000E224488}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="56">
   <si>
     <t>Vendedor</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t xml:space="preserve">Eduardo </t>
+  </si>
+  <si>
+    <t>❌</t>
   </si>
 </sst>
 </file>
@@ -867,8 +870,12 @@
       <c r="D3" s="6">
         <v>3</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G3" s="6">
         <v>2</v>
       </c>
@@ -884,8 +891,12 @@
       <c r="K3" s="6">
         <v>0</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="L3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N3" s="6">
         <v>4</v>
       </c>
@@ -901,8 +912,12 @@
       <c r="R3" s="6">
         <v>2</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
+      <c r="S3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U3" s="6">
         <v>4</v>
       </c>
@@ -918,15 +933,27 @@
       <c r="Y3" s="6">
         <v>4</v>
       </c>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
+      <c r="Z3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB3" s="6">
         <v>6</v>
       </c>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
+      <c r="AC3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
@@ -941,8 +968,12 @@
       <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
@@ -958,8 +989,12 @@
       <c r="K4" s="6">
         <v>0</v>
       </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
+      <c r="L4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N4" s="6">
         <v>0</v>
       </c>
@@ -975,8 +1010,12 @@
       <c r="R4" s="6">
         <v>3</v>
       </c>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
+      <c r="S4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U4" s="6">
         <v>0</v>
       </c>
@@ -992,15 +1031,27 @@
       <c r="Y4" s="6">
         <v>2</v>
       </c>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
+      <c r="Z4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB4" s="6">
         <v>2</v>
       </c>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
+      <c r="AC4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
@@ -1015,8 +1066,12 @@
       <c r="D5" s="6">
         <v>3</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G5" s="6">
         <v>2</v>
       </c>
@@ -1032,8 +1087,12 @@
       <c r="K5" s="6">
         <v>2</v>
       </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
+      <c r="L5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N5" s="6">
         <v>1</v>
       </c>
@@ -1049,8 +1108,12 @@
       <c r="R5" s="6">
         <v>1</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
+      <c r="S5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U5" s="6">
         <v>5</v>
       </c>
@@ -1066,15 +1129,27 @@
       <c r="Y5" s="6">
         <v>2</v>
       </c>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB5" s="6">
         <v>1</v>
       </c>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
+      <c r="AC5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1089,8 +1164,12 @@
       <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G6" s="6">
         <v>1</v>
       </c>
@@ -1106,8 +1185,12 @@
       <c r="K6" s="6">
         <v>0</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N6" s="6">
         <v>3</v>
       </c>
@@ -1123,8 +1206,12 @@
       <c r="R6" s="6">
         <v>2</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
+      <c r="S6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U6" s="6">
         <v>1</v>
       </c>
@@ -1140,15 +1227,27 @@
       <c r="Y6" s="6">
         <v>1</v>
       </c>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
+      <c r="Z6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB6" s="6">
         <v>2</v>
       </c>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
+      <c r="AC6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
@@ -1163,8 +1262,12 @@
       <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="E7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G7" s="6">
         <v>0</v>
       </c>
@@ -1180,8 +1283,12 @@
       <c r="K7" s="6">
         <v>2</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="L7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N7" s="6">
         <v>2</v>
       </c>
@@ -1197,8 +1304,12 @@
       <c r="R7" s="6">
         <v>1</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="S7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U7" s="6">
         <v>4</v>
       </c>
@@ -1214,15 +1325,27 @@
       <c r="Y7" s="6">
         <v>3</v>
       </c>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
+      <c r="Z7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA7" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB7" s="6">
         <v>2</v>
       </c>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
+      <c r="AC7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
@@ -1237,8 +1360,12 @@
       <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="E8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G8" s="6">
         <v>1</v>
       </c>
@@ -1254,8 +1381,12 @@
       <c r="K8" s="6">
         <v>2</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
+      <c r="L8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
@@ -1271,8 +1402,12 @@
       <c r="R8" s="6">
         <v>0</v>
       </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
+      <c r="S8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U8" s="6">
         <v>0</v>
       </c>
@@ -1288,15 +1423,27 @@
       <c r="Y8" s="6">
         <v>0</v>
       </c>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB8" s="6">
         <v>1</v>
       </c>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
+      <c r="AC8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
@@ -1311,8 +1458,12 @@
       <c r="D9" s="6">
         <v>2</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G9" s="6">
         <v>2</v>
       </c>
@@ -1328,8 +1479,12 @@
       <c r="K9" s="6">
         <v>0</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="L9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N9" s="6">
         <v>0</v>
       </c>
@@ -1345,8 +1500,12 @@
       <c r="R9" s="6">
         <v>2</v>
       </c>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
+      <c r="S9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U9" s="6">
         <v>1</v>
       </c>
@@ -1362,15 +1521,27 @@
       <c r="Y9" s="6">
         <v>4</v>
       </c>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
+      <c r="Z9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA9" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB9" s="6">
         <v>4</v>
       </c>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
+      <c r="AC9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
@@ -1385,8 +1556,12 @@
       <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G10" s="6">
         <v>0</v>
       </c>
@@ -1402,8 +1577,12 @@
       <c r="K10" s="6">
         <v>2</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
+      <c r="L10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N10" s="6">
         <v>0</v>
       </c>
@@ -1419,8 +1598,12 @@
       <c r="R10" s="6">
         <v>0</v>
       </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
+      <c r="S10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U10" s="6">
         <v>0</v>
       </c>
@@ -1436,15 +1619,27 @@
       <c r="Y10" s="6">
         <v>0</v>
       </c>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
+      <c r="Z10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB10" s="6">
         <v>0</v>
       </c>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
+      <c r="AC10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
@@ -1459,8 +1654,12 @@
       <c r="D11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G11" s="6">
         <v>1</v>
       </c>
@@ -1476,8 +1675,12 @@
       <c r="K11" s="6">
         <v>1</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c r="L11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N11" s="6">
         <v>3</v>
       </c>
@@ -1493,8 +1696,12 @@
       <c r="R11" s="6">
         <v>0</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
+      <c r="S11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U11" s="6">
         <v>2</v>
       </c>
@@ -1510,15 +1717,27 @@
       <c r="Y11" s="6">
         <v>1</v>
       </c>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
+      <c r="Z11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA11" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB11" s="6">
         <v>1</v>
       </c>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
+      <c r="AC11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -1533,8 +1752,12 @@
       <c r="D12" s="6">
         <v>1</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="E12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="G12" s="6">
         <v>1</v>
       </c>
@@ -1550,8 +1773,12 @@
       <c r="K12" s="6">
         <v>3</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
+      <c r="L12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="N12" s="6">
         <v>1</v>
       </c>
@@ -1567,8 +1794,12 @@
       <c r="R12" s="6">
         <v>3</v>
       </c>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
+      <c r="S12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="U12" s="6">
         <v>2</v>
       </c>
@@ -1584,15 +1815,27 @@
       <c r="Y12" s="6">
         <v>1</v>
       </c>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
+      <c r="Z12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA12" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB12" s="6">
         <v>1</v>
       </c>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
+      <c r="AC12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5B17DA-1C4E-4520-9BCA-7D000E224488}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{674BB15B-6611-415B-880E-10293888A0DC}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30720" yWindow="1815" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -943,7 +943,7 @@
         <v>6</v>
       </c>
       <c r="AC3" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD3" s="6">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>2</v>
       </c>
       <c r="AC4" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4" s="6">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         <v>1</v>
       </c>
       <c r="AC5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" s="6">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="AC6" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD6" s="6">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>2</v>
       </c>
       <c r="AC7" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD7" s="6">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="AC8" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" s="6">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="AC9" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD9" s="6">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="AC11" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD11" s="6">
         <v>0</v>
@@ -1825,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="AC12" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD12" s="6">
         <v>0</v>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{674BB15B-6611-415B-880E-10293888A0DC}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="11_BAEA8D42881876EED39E7A35ADA4D4806B235AC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF691CBD-89A7-4055-8710-55A32C53AF3D}"/>
   <bookViews>
-    <workbookView xWindow="30720" yWindow="1815" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -946,7 +946,7 @@
         <v>4</v>
       </c>
       <c r="AD3" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE3" s="6">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>2</v>
       </c>
       <c r="AD8" s="6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE8" s="6">
         <v>0</v>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C592041-A002-41E4-99A7-8681E5E4DA83}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -619,12 +619,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="32" max="32" width="12.625" customWidth="1"/>
+    <col min="1" max="1" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="32" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -722,7 +723,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -820,7 +821,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -884,8 +885,11 @@
       <c r="AC3">
         <v>4</v>
       </c>
+      <c r="AD3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -949,8 +953,11 @@
       <c r="AC4">
         <v>3</v>
       </c>
+      <c r="AD4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>66</v>
       </c>
@@ -1014,8 +1021,11 @@
       <c r="AC5">
         <v>1</v>
       </c>
+      <c r="AD5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -1079,8 +1089,11 @@
       <c r="AC6">
         <v>3</v>
       </c>
+      <c r="AD6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>68</v>
       </c>
@@ -1144,8 +1157,11 @@
       <c r="AC7">
         <v>3</v>
       </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -1209,8 +1225,11 @@
       <c r="AC8">
         <v>2</v>
       </c>
+      <c r="AD8">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -1274,8 +1293,11 @@
       <c r="AC9">
         <v>2</v>
       </c>
+      <c r="AD9">
+        <v>6</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1310,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1339,8 +1361,11 @@
       <c r="AC10">
         <v>0</v>
       </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -1404,8 +1429,11 @@
       <c r="AC11">
         <v>2</v>
       </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>73</v>
       </c>
@@ -1468,6 +1496,9 @@
       </c>
       <c r="AC12">
         <v>5</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C592041-A002-41E4-99A7-8681E5E4DA83}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C17253C8-2339-4C58-83F6-3CC600716C93}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -888,6 +888,9 @@
       <c r="AD3">
         <v>2</v>
       </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -956,6 +959,9 @@
       <c r="AD4">
         <v>2</v>
       </c>
+      <c r="AE4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1024,6 +1030,9 @@
       <c r="AD5">
         <v>5</v>
       </c>
+      <c r="AE5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1092,6 +1101,9 @@
       <c r="AD6">
         <v>2</v>
       </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1160,6 +1172,9 @@
       <c r="AD7">
         <v>1</v>
       </c>
+      <c r="AE7">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1228,6 +1243,9 @@
       <c r="AD8">
         <v>2</v>
       </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1296,6 +1314,9 @@
       <c r="AD9">
         <v>6</v>
       </c>
+      <c r="AE9">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1364,6 +1385,9 @@
       <c r="AD10">
         <v>0</v>
       </c>
+      <c r="AE10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1432,6 +1456,9 @@
       <c r="AD11">
         <v>1</v>
       </c>
+      <c r="AE11">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1498,6 +1525,9 @@
         <v>5</v>
       </c>
       <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
         <v>0</v>
       </c>
     </row>

--- a/propostas.xlsx
+++ b/propostas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://concresupersc-my.sharepoint.com/personal/marketing_concresupersc_onmicrosoft_com/Documents/Área de Trabalho/C.I.V/Dashbord/Propostas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C17253C8-2339-4C58-83F6-3CC600716C93}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{F1A93860-B310-434D-8393-DB0C8680B723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590D1248-920F-4975-A8D5-1EFA953B7E74}"/>
   <bookViews>
-    <workbookView xWindow="34785" yWindow="-3135" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Propostas" sheetId="1" r:id="rId1"/>
@@ -891,6 +891,9 @@
       <c r="AE3">
         <v>1</v>
       </c>
+      <c r="AF3">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -962,6 +965,9 @@
       <c r="AE4">
         <v>2</v>
       </c>
+      <c r="AF4">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1033,6 +1039,9 @@
       <c r="AE5">
         <v>2</v>
       </c>
+      <c r="AF5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1104,6 +1113,9 @@
       <c r="AE6">
         <v>0</v>
       </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1175,6 +1187,9 @@
       <c r="AE7">
         <v>5</v>
       </c>
+      <c r="AF7">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1246,6 +1261,9 @@
       <c r="AE8">
         <v>1</v>
       </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1317,6 +1335,9 @@
       <c r="AE9">
         <v>2</v>
       </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1388,6 +1409,9 @@
       <c r="AE10">
         <v>2</v>
       </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1459,6 +1483,9 @@
       <c r="AE11">
         <v>2</v>
       </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1529,6 +1556,9 @@
       </c>
       <c r="AE12">
         <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
